--- a/assets/files/templates/SafePlum_sop.xlsx
+++ b/assets/files/templates/SafePlum_sop.xlsx
@@ -8929,12 +8929,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
@@ -8947,7 +8947,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
         <v>7</v>
       </c>
@@ -8960,32 +8960,32 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
         <v>14</v>
       </c>
@@ -8998,17 +8998,17 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
         <v>18</v>
       </c>
@@ -9021,12 +9021,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
         <v>21</v>
       </c>
